--- a/dataset_sosanh3rag.xlsx
+++ b/dataset_sosanh3rag.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\Documents\PTMNM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Deepseek-Rag-Agent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{450D83C5-AB54-4EE8-A2BE-63D5572CE9D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{472E8CC0-F205-45F2-A479-5B68DA5DBF52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3953,11 +3953,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A15:K15"/>
-    <mergeCell ref="A16:K16"/>
-    <mergeCell ref="A17:K17"/>
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="A2:XFD2"/>
     <mergeCell ref="A22:K22"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A4:K4"/>
@@ -3974,6 +3969,11 @@
     <mergeCell ref="A21:K21"/>
     <mergeCell ref="A13:K13"/>
     <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A16:K16"/>
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="A2:XFD2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
